--- a/Sina/stock_codes.xlsx
+++ b/Sina/stock_codes.xlsx
@@ -4,11 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="16580"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$437</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,51 +30,1287 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="437">
   <si>
     <t>stock_code</t>
   </si>
   <si>
+    <t>sh000001</t>
+  </si>
+  <si>
+    <t>sh000012</t>
+  </si>
+  <si>
+    <t>sh600006</t>
+  </si>
+  <si>
+    <t>sh600009</t>
+  </si>
+  <si>
+    <t>sh600027</t>
+  </si>
+  <si>
+    <t>sh600037</t>
+  </si>
+  <si>
+    <t>sh600039</t>
+  </si>
+  <si>
+    <t>sh600053</t>
+  </si>
+  <si>
+    <t>sh600054</t>
+  </si>
+  <si>
+    <t>sh600055</t>
+  </si>
+  <si>
+    <t>sh600058</t>
+  </si>
+  <si>
+    <t>sh600089</t>
+  </si>
+  <si>
+    <t>sh600098</t>
+  </si>
+  <si>
+    <t>sh600119</t>
+  </si>
+  <si>
+    <t>sh600132</t>
+  </si>
+  <si>
+    <t>sh600135</t>
+  </si>
+  <si>
+    <t>sh600143</t>
+  </si>
+  <si>
+    <t>sh600148</t>
+  </si>
+  <si>
+    <t>sh600153</t>
+  </si>
+  <si>
+    <t>sh600157</t>
+  </si>
+  <si>
+    <t>sh600176</t>
+  </si>
+  <si>
+    <t>sh600177</t>
+  </si>
+  <si>
+    <t>sh600185</t>
+  </si>
+  <si>
+    <t>sh600198</t>
+  </si>
+  <si>
+    <t>sh600206</t>
+  </si>
+  <si>
+    <t>sh600212</t>
+  </si>
+  <si>
+    <t>sh600230</t>
+  </si>
+  <si>
+    <t>sh600235</t>
+  </si>
+  <si>
+    <t>sh600268</t>
+  </si>
+  <si>
+    <t>sh600271</t>
+  </si>
+  <si>
+    <t>sh600280</t>
+  </si>
+  <si>
+    <t>sh600283</t>
+  </si>
+  <si>
+    <t>sh600292</t>
+  </si>
+  <si>
+    <t>sh600305</t>
+  </si>
+  <si>
+    <t>sh600336</t>
+  </si>
+  <si>
+    <t>sh600338</t>
+  </si>
+  <si>
+    <t>sh600340</t>
+  </si>
+  <si>
+    <t>sh600392</t>
+  </si>
+  <si>
+    <t>sh600408</t>
+  </si>
+  <si>
+    <t>sh600435</t>
+  </si>
+  <si>
+    <t>sh600477</t>
+  </si>
+  <si>
+    <t>sh600489</t>
+  </si>
+  <si>
+    <t>sh600497</t>
+  </si>
+  <si>
+    <t>sh600507</t>
+  </si>
+  <si>
+    <t>sh600518</t>
+  </si>
+  <si>
+    <t>sh600522</t>
+  </si>
+  <si>
+    <t>sh600523</t>
+  </si>
+  <si>
+    <t>sh600529</t>
+  </si>
+  <si>
+    <t>sh600536</t>
+  </si>
+  <si>
+    <t>sh600546</t>
+  </si>
+  <si>
+    <t>sh600548</t>
+  </si>
+  <si>
+    <t>sh600550</t>
+  </si>
+  <si>
+    <t>sh600558</t>
+  </si>
+  <si>
+    <t>sh600563</t>
+  </si>
+  <si>
+    <t>sh600579</t>
+  </si>
+  <si>
+    <t>sh600584</t>
+  </si>
+  <si>
+    <t>sh600587</t>
+  </si>
+  <si>
+    <t>sh600588</t>
+  </si>
+  <si>
+    <t>sh600616</t>
+  </si>
+  <si>
+    <t>sh600621</t>
+  </si>
+  <si>
+    <t>sh600622</t>
+  </si>
+  <si>
+    <t>sh600635</t>
+  </si>
+  <si>
+    <t>sh600675</t>
+  </si>
+  <si>
+    <t>sh600694</t>
+  </si>
+  <si>
+    <t>sh600702</t>
+  </si>
+  <si>
+    <t>sh600706</t>
+  </si>
+  <si>
+    <t>sh600712</t>
+  </si>
+  <si>
+    <t>sh600724</t>
+  </si>
+  <si>
+    <t>sh600729</t>
+  </si>
+  <si>
+    <t>sh600739</t>
+  </si>
+  <si>
+    <t>sh600748</t>
+  </si>
+  <si>
+    <t>sh600754</t>
+  </si>
+  <si>
+    <t>sh600756</t>
+  </si>
+  <si>
+    <t>sh600757</t>
+  </si>
+  <si>
+    <t>sh600764</t>
+  </si>
+  <si>
+    <t>sh600789</t>
+  </si>
+  <si>
+    <t>sh600797</t>
+  </si>
+  <si>
+    <t>sh600829</t>
+  </si>
+  <si>
+    <t>sh600838</t>
+  </si>
+  <si>
+    <t>sh600871</t>
+  </si>
+  <si>
+    <t>sh600872</t>
+  </si>
+  <si>
+    <t>sh600875</t>
+  </si>
+  <si>
+    <t>sh600895</t>
+  </si>
+  <si>
+    <t>sh600903</t>
+  </si>
+  <si>
+    <t>sh600963</t>
+  </si>
+  <si>
+    <t>sh600976</t>
+  </si>
+  <si>
+    <t>sh600984</t>
+  </si>
+  <si>
+    <t>sh600988</t>
+  </si>
+  <si>
+    <t>sh601000</t>
+  </si>
+  <si>
+    <t>sh601010</t>
+  </si>
+  <si>
+    <t>sh601021</t>
+  </si>
+  <si>
+    <t>sh601061</t>
+  </si>
+  <si>
+    <t>sh601086</t>
+  </si>
+  <si>
+    <t>sh601106</t>
+  </si>
+  <si>
+    <t>sh601108</t>
+  </si>
+  <si>
+    <t>sh601136</t>
+  </si>
+  <si>
+    <t>sh601139</t>
+  </si>
+  <si>
+    <t>sh601155</t>
+  </si>
+  <si>
+    <t>sh601162</t>
+  </si>
+  <si>
+    <t>sh601198</t>
+  </si>
+  <si>
+    <t>sh601216</t>
+  </si>
+  <si>
+    <t>sh601369</t>
+  </si>
+  <si>
+    <t>sh601566</t>
+  </si>
+  <si>
+    <t>sh601608</t>
+  </si>
+  <si>
+    <t>sh601665</t>
+  </si>
+  <si>
+    <t>sh601669</t>
+  </si>
+  <si>
+    <t>sh601702</t>
+  </si>
+  <si>
+    <t>sh601778</t>
+  </si>
+  <si>
+    <t>sh601788</t>
+  </si>
+  <si>
+    <t>sh601877</t>
+  </si>
+  <si>
+    <t>sh601890</t>
+  </si>
+  <si>
+    <t>sh601916</t>
+  </si>
+  <si>
+    <t>sh601933</t>
+  </si>
+  <si>
+    <t>sh601975</t>
+  </si>
+  <si>
+    <t>sh601990</t>
+  </si>
+  <si>
+    <t>sh603002</t>
+  </si>
+  <si>
+    <t>sh603005</t>
+  </si>
+  <si>
+    <t>sh603010</t>
+  </si>
+  <si>
+    <t>sh603025</t>
+  </si>
+  <si>
+    <t>sh603030</t>
+  </si>
+  <si>
+    <t>sh603048</t>
+  </si>
+  <si>
+    <t>sh603055</t>
+  </si>
+  <si>
+    <t>sh603058</t>
+  </si>
+  <si>
+    <t>sh603061</t>
+  </si>
+  <si>
+    <t>sh603063</t>
+  </si>
+  <si>
+    <t>sh603160</t>
+  </si>
+  <si>
+    <t>sh603168</t>
+  </si>
+  <si>
+    <t>sh603188</t>
+  </si>
+  <si>
+    <t>sh603197</t>
+  </si>
+  <si>
+    <t>sh603239</t>
+  </si>
+  <si>
+    <t>sh603259</t>
+  </si>
+  <si>
+    <t>sh603260</t>
+  </si>
+  <si>
+    <t>sh603307</t>
+  </si>
+  <si>
+    <t>sh603316</t>
+  </si>
+  <si>
+    <t>sh603456</t>
+  </si>
+  <si>
+    <t>sh603477</t>
+  </si>
+  <si>
+    <t>sh603601</t>
+  </si>
+  <si>
+    <t>sh603602</t>
+  </si>
+  <si>
+    <t>sh603661</t>
+  </si>
+  <si>
+    <t>sh603667</t>
+  </si>
+  <si>
+    <t>sh603706</t>
+  </si>
+  <si>
+    <t>sh603717</t>
+  </si>
+  <si>
+    <t>sh603790</t>
+  </si>
+  <si>
+    <t>sh603799</t>
+  </si>
+  <si>
+    <t>sh603810</t>
+  </si>
+  <si>
+    <t>sh603816</t>
+  </si>
+  <si>
+    <t>sh603880</t>
+  </si>
+  <si>
+    <t>sh603881</t>
+  </si>
+  <si>
+    <t>sh603885</t>
+  </si>
+  <si>
+    <t>sh603888</t>
+  </si>
+  <si>
+    <t>sh603893</t>
+  </si>
+  <si>
+    <t>sh603949</t>
+  </si>
+  <si>
+    <t>sh603969</t>
+  </si>
+  <si>
+    <t>sh603976</t>
+  </si>
+  <si>
+    <t>sh603989</t>
+  </si>
+  <si>
+    <t>sh605001</t>
+  </si>
+  <si>
+    <t>sh605008</t>
+  </si>
+  <si>
+    <t>sh605117</t>
+  </si>
+  <si>
+    <t>sh605177</t>
+  </si>
+  <si>
+    <t>sh688005</t>
+  </si>
+  <si>
+    <t>sh688017</t>
+  </si>
+  <si>
+    <t>sh688063</t>
+  </si>
+  <si>
+    <t>sh688070</t>
+  </si>
+  <si>
+    <t>sh688099</t>
+  </si>
+  <si>
+    <t>sh688169</t>
+  </si>
+  <si>
+    <t>sh688190</t>
+  </si>
+  <si>
+    <t>sh688231</t>
+  </si>
+  <si>
+    <t>sh688308</t>
+  </si>
+  <si>
+    <t>sh688316</t>
+  </si>
+  <si>
+    <t>sh688400</t>
+  </si>
+  <si>
+    <t>sh688418</t>
+  </si>
+  <si>
+    <t>sh688531</t>
+  </si>
+  <si>
+    <t>sh688556</t>
+  </si>
+  <si>
+    <t>sh688567</t>
+  </si>
+  <si>
+    <t>sh688660</t>
+  </si>
+  <si>
+    <t>sh688721</t>
+  </si>
+  <si>
+    <t>sh689009</t>
+  </si>
+  <si>
+    <t>sh900925</t>
+  </si>
+  <si>
+    <t>sz000009</t>
+  </si>
+  <si>
+    <t>sz000011</t>
+  </si>
+  <si>
+    <t>sz000021</t>
+  </si>
+  <si>
+    <t>sz000025</t>
+  </si>
+  <si>
+    <t>sz000029</t>
+  </si>
+  <si>
+    <t>sz000039</t>
+  </si>
+  <si>
+    <t>sz000049</t>
+  </si>
+  <si>
+    <t>sz000066</t>
+  </si>
+  <si>
+    <t>sz000078</t>
+  </si>
+  <si>
+    <t>sz000156</t>
+  </si>
+  <si>
+    <t>sz000410</t>
+  </si>
+  <si>
+    <t>sz000513</t>
+  </si>
+  <si>
+    <t>sz000519</t>
+  </si>
+  <si>
+    <t>sz000526</t>
+  </si>
+  <si>
+    <t>sz000528</t>
+  </si>
+  <si>
+    <t>sz000529</t>
+  </si>
+  <si>
+    <t>sz000555</t>
+  </si>
+  <si>
+    <t>sz000568</t>
+  </si>
+  <si>
+    <t>sz000596</t>
+  </si>
+  <si>
+    <t>sz000628</t>
+  </si>
+  <si>
+    <t>sz000650</t>
+  </si>
+  <si>
+    <t>sz000661</t>
+  </si>
+  <si>
+    <t>sz000686</t>
+  </si>
+  <si>
+    <t>sz000700</t>
+  </si>
+  <si>
+    <t>sz000723</t>
+  </si>
+  <si>
+    <t>sz000733</t>
+  </si>
+  <si>
+    <t>sz000735</t>
+  </si>
+  <si>
+    <t>sz000738</t>
+  </si>
+  <si>
+    <t>sz000739</t>
+  </si>
+  <si>
+    <t>sz000777</t>
+  </si>
+  <si>
+    <t>sz000782</t>
+  </si>
+  <si>
+    <t>sz000791</t>
+  </si>
+  <si>
+    <t>sz000799</t>
+  </si>
+  <si>
+    <t>sz000810</t>
+  </si>
+  <si>
+    <t>sz000816</t>
+  </si>
+  <si>
+    <t>sz000821</t>
+  </si>
+  <si>
+    <t>sz000831</t>
+  </si>
+  <si>
+    <t>sz000839</t>
+  </si>
+  <si>
+    <t>sz000858</t>
+  </si>
+  <si>
+    <t>sz000868</t>
+  </si>
+  <si>
+    <t>sz000905</t>
+  </si>
+  <si>
+    <t>sz000932</t>
+  </si>
+  <si>
+    <t>sz000963</t>
+  </si>
+  <si>
+    <t>sz000980</t>
+  </si>
+  <si>
+    <t>sz001259</t>
+  </si>
+  <si>
+    <t>sz001299</t>
+  </si>
+  <si>
+    <t>sz001337</t>
+  </si>
+  <si>
+    <t>sz001914</t>
+  </si>
+  <si>
+    <t>sz002006</t>
+  </si>
+  <si>
+    <t>sz002007</t>
+  </si>
+  <si>
+    <t>sz002008</t>
+  </si>
+  <si>
+    <t>sz002014</t>
+  </si>
+  <si>
+    <t>sz002023</t>
+  </si>
+  <si>
+    <t>sz002035</t>
+  </si>
+  <si>
+    <t>sz002037</t>
+  </si>
+  <si>
+    <t>sz002043</t>
+  </si>
+  <si>
+    <t>sz002049</t>
+  </si>
+  <si>
+    <t>sz002067</t>
+  </si>
+  <si>
+    <t>sz002074</t>
+  </si>
+  <si>
+    <t>sz002081</t>
+  </si>
+  <si>
+    <t>sz002086</t>
+  </si>
+  <si>
+    <t>sz002095</t>
+  </si>
+  <si>
+    <t>sz002104</t>
+  </si>
+  <si>
+    <t>sz002112</t>
+  </si>
+  <si>
+    <t>sz002120</t>
+  </si>
+  <si>
+    <t>sz002127</t>
+  </si>
+  <si>
+    <t>sz002128</t>
+  </si>
+  <si>
+    <t>sz002130</t>
+  </si>
+  <si>
+    <t>sz002131</t>
+  </si>
+  <si>
+    <t>sz002153</t>
+  </si>
+  <si>
+    <t>sz002160</t>
+  </si>
+  <si>
+    <t>sz002163</t>
+  </si>
+  <si>
+    <t>sz002167</t>
+  </si>
+  <si>
+    <t>sz002169</t>
+  </si>
+  <si>
+    <t>sz002183</t>
+  </si>
+  <si>
+    <t>sz002185</t>
+  </si>
+  <si>
+    <t>sz002190</t>
+  </si>
+  <si>
+    <t>sz002195</t>
+  </si>
+  <si>
+    <t>sz002204</t>
+  </si>
+  <si>
+    <t>sz002218</t>
+  </si>
+  <si>
+    <t>sz002223</t>
+  </si>
+  <si>
+    <t>sz002233</t>
+  </si>
+  <si>
+    <t>sz002236</t>
+  </si>
+  <si>
+    <t>sz002237</t>
+  </si>
+  <si>
+    <t>sz002239</t>
+  </si>
+  <si>
+    <t>sz002272</t>
+  </si>
+  <si>
+    <t>sz002276</t>
+  </si>
+  <si>
+    <t>sz002291</t>
+  </si>
+  <si>
+    <t>sz002292</t>
+  </si>
+  <si>
+    <t>sz002294</t>
+  </si>
+  <si>
+    <t>sz002306</t>
+  </si>
+  <si>
+    <t>sz002320</t>
+  </si>
+  <si>
+    <t>sz002326</t>
+  </si>
+  <si>
+    <t>sz002328</t>
+  </si>
+  <si>
+    <t>sz002343</t>
+  </si>
+  <si>
+    <t>sz002347</t>
+  </si>
+  <si>
+    <t>sz002353</t>
+  </si>
+  <si>
+    <t>sz002355</t>
+  </si>
+  <si>
+    <t>sz002358</t>
+  </si>
+  <si>
+    <t>sz002369</t>
+  </si>
+  <si>
+    <t>sz002396</t>
+  </si>
+  <si>
+    <t>sz002430</t>
+  </si>
+  <si>
+    <t>sz002439</t>
+  </si>
+  <si>
+    <t>sz002445</t>
+  </si>
+  <si>
+    <t>sz002448</t>
+  </si>
+  <si>
+    <t>sz002458</t>
+  </si>
+  <si>
+    <t>sz002460</t>
+  </si>
+  <si>
+    <t>sz002466</t>
+  </si>
+  <si>
+    <t>sz002475</t>
+  </si>
+  <si>
+    <t>sz002497</t>
+  </si>
+  <si>
+    <t>sz002530</t>
+  </si>
+  <si>
+    <t>sz002545</t>
+  </si>
+  <si>
+    <t>sz002548</t>
+  </si>
+  <si>
+    <t>sz002549</t>
+  </si>
+  <si>
+    <t>sz002555</t>
+  </si>
+  <si>
+    <t>sz002559</t>
+  </si>
+  <si>
+    <t>sz002572</t>
+  </si>
+  <si>
+    <t>sz002573</t>
+  </si>
+  <si>
+    <t>sz002600</t>
+  </si>
+  <si>
+    <t>sz002601</t>
+  </si>
+  <si>
+    <t>sz002602</t>
+  </si>
+  <si>
+    <t>sz002628</t>
+  </si>
+  <si>
+    <t>sz002629</t>
+  </si>
+  <si>
+    <t>sz002646</t>
+  </si>
+  <si>
+    <t>sz002648</t>
+  </si>
+  <si>
+    <t>sz002651</t>
+  </si>
+  <si>
+    <t>sz002654</t>
+  </si>
+  <si>
+    <t>sz002655</t>
+  </si>
+  <si>
+    <t>sz002660</t>
+  </si>
+  <si>
+    <t>sz002669</t>
+  </si>
+  <si>
+    <t>sz002673</t>
+  </si>
+  <si>
+    <t>sz002677</t>
+  </si>
+  <si>
+    <t>sz002745</t>
+  </si>
+  <si>
+    <t>sz002747</t>
+  </si>
+  <si>
+    <t>sz002756</t>
+  </si>
+  <si>
+    <t>sz002795</t>
+  </si>
+  <si>
+    <t>sz002812</t>
+  </si>
+  <si>
+    <t>sz002821</t>
+  </si>
+  <si>
+    <t>sz002843</t>
+  </si>
+  <si>
+    <t>sz002903</t>
+  </si>
+  <si>
+    <t>sz002908</t>
+  </si>
+  <si>
+    <t>sz002909</t>
+  </si>
+  <si>
+    <t>sz002932</t>
+  </si>
+  <si>
+    <t>sz002936</t>
+  </si>
+  <si>
+    <t>sz002940</t>
+  </si>
+  <si>
+    <t>sz002943</t>
+  </si>
+  <si>
+    <t>sz002959</t>
+  </si>
+  <si>
+    <t>sz002965</t>
+  </si>
+  <si>
+    <t>sz002972</t>
+  </si>
+  <si>
+    <t>sz002985</t>
+  </si>
+  <si>
+    <t>sz003001</t>
+  </si>
+  <si>
+    <t>sz003025</t>
+  </si>
+  <si>
+    <t>sz300001</t>
+  </si>
+  <si>
+    <t>sz300008</t>
+  </si>
+  <si>
+    <t>sz300017</t>
+  </si>
+  <si>
+    <t>sz300020</t>
+  </si>
+  <si>
+    <t>sz300024</t>
+  </si>
+  <si>
+    <t>sz300051</t>
+  </si>
+  <si>
+    <t>sz300055</t>
+  </si>
+  <si>
+    <t>sz300056</t>
+  </si>
+  <si>
+    <t>sz300061</t>
+  </si>
+  <si>
+    <t>sz300083</t>
+  </si>
+  <si>
+    <t>sz300084</t>
+  </si>
+  <si>
+    <t>sz300122</t>
+  </si>
+  <si>
+    <t>sz300145</t>
+  </si>
+  <si>
+    <t>sz300146</t>
+  </si>
+  <si>
+    <t>sz300149</t>
+  </si>
+  <si>
+    <t>sz300166</t>
+  </si>
+  <si>
+    <t>sz300175</t>
+  </si>
+  <si>
+    <t>sz300180</t>
+  </si>
+  <si>
+    <t>sz300198</t>
+  </si>
+  <si>
+    <t>sz300212</t>
+  </si>
+  <si>
+    <t>sz300221</t>
+  </si>
+  <si>
     <t>sz300243</t>
   </si>
   <si>
+    <t>sz300271</t>
+  </si>
+  <si>
+    <t>sz300278</t>
+  </si>
+  <si>
+    <t>sz300285</t>
+  </si>
+  <si>
     <t>sz300315</t>
   </si>
   <si>
-    <t>sh688070</t>
-  </si>
-  <si>
-    <t>sh601788</t>
-  </si>
-  <si>
-    <t>sz000519</t>
-  </si>
-  <si>
-    <t>sh603601</t>
+    <t>sz300316</t>
+  </si>
+  <si>
+    <t>sz300322</t>
+  </si>
+  <si>
+    <t>sz300339</t>
+  </si>
+  <si>
+    <t>sz300343</t>
+  </si>
+  <si>
+    <t>sz300346</t>
+  </si>
+  <si>
+    <t>sz300355</t>
+  </si>
+  <si>
+    <t>sz300383</t>
+  </si>
+  <si>
+    <t>sz300397</t>
+  </si>
+  <si>
+    <t>sz300407</t>
+  </si>
+  <si>
+    <t>sz300416</t>
+  </si>
+  <si>
+    <t>sz300424</t>
+  </si>
+  <si>
+    <t>sz300430</t>
   </si>
   <si>
     <t>sz300444</t>
   </si>
   <si>
+    <t>sz300450</t>
+  </si>
+  <si>
+    <t>sz300454</t>
+  </si>
+  <si>
+    <t>sz300458</t>
+  </si>
+  <si>
     <t>sz300461</t>
   </si>
   <si>
-    <t>sz002972</t>
-  </si>
-  <si>
-    <t>sh601162</t>
-  </si>
-  <si>
-    <t>sz000686</t>
-  </si>
-  <si>
-    <t>sz000963</t>
-  </si>
-  <si>
-    <t>sz001259</t>
-  </si>
-  <si>
-    <t>sh603307</t>
+    <t>sz300467</t>
+  </si>
+  <si>
+    <t>sz300469</t>
+  </si>
+  <si>
+    <t>sz300471</t>
+  </si>
+  <si>
+    <t>sz300491</t>
+  </si>
+  <si>
+    <t>sz300496</t>
+  </si>
+  <si>
+    <t>sz300503</t>
+  </si>
+  <si>
+    <t>sz300506</t>
+  </si>
+  <si>
+    <t>sz300525</t>
+  </si>
+  <si>
+    <t>sz300529</t>
+  </si>
+  <si>
+    <t>sz300542</t>
+  </si>
+  <si>
+    <t>sz300564</t>
+  </si>
+  <si>
+    <t>sz300569</t>
+  </si>
+  <si>
+    <t>sz300579</t>
+  </si>
+  <si>
+    <t>sz300596</t>
+  </si>
+  <si>
+    <t>sz300601</t>
+  </si>
+  <si>
+    <t>sz300618</t>
+  </si>
+  <si>
+    <t>sz300624</t>
+  </si>
+  <si>
+    <t>sz300625</t>
+  </si>
+  <si>
+    <t>sz300628</t>
+  </si>
+  <si>
+    <t>sz300636</t>
+  </si>
+  <si>
+    <t>sz300648</t>
+  </si>
+  <si>
+    <t>sz300664</t>
+  </si>
+  <si>
+    <t>sz300671</t>
+  </si>
+  <si>
+    <t>sz300674</t>
+  </si>
+  <si>
+    <t>sz300676</t>
+  </si>
+  <si>
+    <t>sz300677</t>
+  </si>
+  <si>
+    <t>sz300682</t>
+  </si>
+  <si>
+    <t>sz300686</t>
+  </si>
+  <si>
+    <t>sz300693</t>
+  </si>
+  <si>
+    <t>sz300705</t>
+  </si>
+  <si>
+    <t>sz300710</t>
+  </si>
+  <si>
+    <t>sz300711</t>
+  </si>
+  <si>
+    <t>sz300713</t>
+  </si>
+  <si>
+    <t>sz300735</t>
+  </si>
+  <si>
+    <t>sz300741</t>
+  </si>
+  <si>
+    <t>sz300747</t>
+  </si>
+  <si>
+    <t>sz300751</t>
+  </si>
+  <si>
+    <t>sz300767</t>
+  </si>
+  <si>
+    <t>sz300769</t>
+  </si>
+  <si>
+    <t>sz300773</t>
+  </si>
+  <si>
+    <t>sz300796</t>
+  </si>
+  <si>
+    <t>sz300807</t>
+  </si>
+  <si>
+    <t>sz300809</t>
+  </si>
+  <si>
+    <t>sz300829</t>
+  </si>
+  <si>
+    <t>sz300832</t>
+  </si>
+  <si>
+    <t>sz300833</t>
+  </si>
+  <si>
+    <t>sz300836</t>
+  </si>
+  <si>
+    <t>sz300842</t>
+  </si>
+  <si>
+    <t>sz300869</t>
+  </si>
+  <si>
+    <t>sz300943</t>
+  </si>
+  <si>
+    <t>sz300963</t>
+  </si>
+  <si>
+    <t>sz300995</t>
+  </si>
+  <si>
+    <t>sz301107</t>
   </si>
   <si>
     <t>sz301227</t>
@@ -80,1282 +1319,28 @@
     <t>sz301234</t>
   </si>
   <si>
+    <t>sz301251</t>
+  </si>
+  <si>
+    <t>sz301257</t>
+  </si>
+  <si>
+    <t>sz301287</t>
+  </si>
+  <si>
+    <t>sz301359</t>
+  </si>
+  <si>
     <t>sz301388</t>
   </si>
   <si>
-    <t>sh600392</t>
-  </si>
-  <si>
-    <t>sz002965</t>
-  </si>
-  <si>
-    <t>sz000733</t>
-  </si>
-  <si>
-    <t>sz300542</t>
-  </si>
-  <si>
-    <t>sz002195</t>
-  </si>
-  <si>
-    <t>sh600739</t>
-  </si>
-  <si>
-    <t>sz001299</t>
-  </si>
-  <si>
-    <t>sz002548</t>
-  </si>
-  <si>
-    <t>sh688017</t>
-  </si>
-  <si>
-    <t>sz300166</t>
-  </si>
-  <si>
-    <t>sz002628</t>
-  </si>
-  <si>
-    <t>sh688316</t>
-  </si>
-  <si>
-    <t>sz301107</t>
-  </si>
-  <si>
-    <t>sh688099</t>
-  </si>
-  <si>
-    <t>sz002439</t>
-  </si>
-  <si>
-    <t>sh600523</t>
-  </si>
-  <si>
-    <t>sz002677</t>
-  </si>
-  <si>
-    <t>sz300430</t>
-  </si>
-  <si>
-    <t>sz002355</t>
-  </si>
-  <si>
-    <t>sh600838</t>
-  </si>
-  <si>
-    <t>sz002646</t>
-  </si>
-  <si>
-    <t>sz000738</t>
-  </si>
-  <si>
-    <t>sz000777</t>
-  </si>
-  <si>
-    <t>sh688418</t>
-  </si>
-  <si>
-    <t>sh600039</t>
-  </si>
-  <si>
-    <t>sz301251</t>
-  </si>
-  <si>
-    <t>sh603893</t>
-  </si>
-  <si>
-    <t>sz300346</t>
-  </si>
-  <si>
-    <t>sh600621</t>
-  </si>
-  <si>
-    <t>sh603055</t>
-  </si>
-  <si>
-    <t>sh000001</t>
-  </si>
-  <si>
-    <t>sz301359</t>
-  </si>
-  <si>
-    <t>sh600185</t>
-  </si>
-  <si>
-    <t>sz002475</t>
-  </si>
-  <si>
-    <t>sz300671</t>
-  </si>
-  <si>
-    <t>sh603259</t>
-  </si>
-  <si>
-    <t>sh000012</t>
-  </si>
-  <si>
-    <t>sh605117</t>
-  </si>
-  <si>
-    <t>sh605177</t>
-  </si>
-  <si>
-    <t>sh603188</t>
-  </si>
-  <si>
-    <t>sh600230</t>
-  </si>
-  <si>
-    <t>sz002008</t>
-  </si>
-  <si>
-    <t>sz300564</t>
-  </si>
-  <si>
-    <t>sh601702</t>
-  </si>
-  <si>
-    <t>sz003001</t>
-  </si>
-  <si>
-    <t>sz300809</t>
-  </si>
-  <si>
-    <t>sh603477</t>
+    <t>sz301503</t>
+  </si>
+  <si>
+    <t>sz301512</t>
   </si>
   <si>
     <t>sz301525</t>
-  </si>
-  <si>
-    <t>sz002985</t>
-  </si>
-  <si>
-    <t>sz300503</t>
-  </si>
-  <si>
-    <t>sz300842</t>
-  </si>
-  <si>
-    <t>sh688721</t>
-  </si>
-  <si>
-    <t>sz300693</t>
-  </si>
-  <si>
-    <t>sh689009</t>
-  </si>
-  <si>
-    <t>sz003025</t>
-  </si>
-  <si>
-    <t>sz301512</t>
-  </si>
-  <si>
-    <t>sz002006</t>
-  </si>
-  <si>
-    <t>sz002014</t>
-  </si>
-  <si>
-    <t>sh600694</t>
-  </si>
-  <si>
-    <t>sh688556</t>
-  </si>
-  <si>
-    <t>sh688308</t>
-  </si>
-  <si>
-    <t>sh688531</t>
-  </si>
-  <si>
-    <t>sh600518</t>
-  </si>
-  <si>
-    <t>sz300624</t>
-  </si>
-  <si>
-    <t>sh603048</t>
-  </si>
-  <si>
-    <t>sh600292</t>
-  </si>
-  <si>
-    <t>sz002023</t>
-  </si>
-  <si>
-    <t>sz300416</t>
-  </si>
-  <si>
-    <t>sz000868</t>
-  </si>
-  <si>
-    <t>sz300322</t>
-  </si>
-  <si>
-    <t>sh600579</t>
-  </si>
-  <si>
-    <t>sz300713</t>
-  </si>
-  <si>
-    <t>sz301503</t>
-  </si>
-  <si>
-    <t>sh600212</t>
-  </si>
-  <si>
-    <t>sz300491</t>
-  </si>
-  <si>
-    <t>sz002037</t>
-  </si>
-  <si>
-    <t>sz002602</t>
-  </si>
-  <si>
-    <t>sh601061</t>
-  </si>
-  <si>
-    <t>sz300995</t>
-  </si>
-  <si>
-    <t>sz300355</t>
-  </si>
-  <si>
-    <t>sz001337</t>
-  </si>
-  <si>
-    <t>sh600895</t>
-  </si>
-  <si>
-    <t>sh603168</t>
-  </si>
-  <si>
-    <t>sz300056</t>
-  </si>
-  <si>
-    <t>sz002756</t>
-  </si>
-  <si>
-    <t>sz002651</t>
-  </si>
-  <si>
-    <t>sz301257</t>
-  </si>
-  <si>
-    <t>sh600054</t>
-  </si>
-  <si>
-    <t>sz300625</t>
-  </si>
-  <si>
-    <t>sh600706</t>
-  </si>
-  <si>
-    <t>sh603061</t>
-  </si>
-  <si>
-    <t>sh601136</t>
-  </si>
-  <si>
-    <t>sh600616</t>
-  </si>
-  <si>
-    <t>sz000528</t>
-  </si>
-  <si>
-    <t>sh688231</t>
-  </si>
-  <si>
-    <t>sh688400</t>
-  </si>
-  <si>
-    <t>sz300383</t>
-  </si>
-  <si>
-    <t>sz300145</t>
-  </si>
-  <si>
-    <t>sh688190</t>
-  </si>
-  <si>
-    <t>sz002204</t>
-  </si>
-  <si>
-    <t>sz300618</t>
-  </si>
-  <si>
-    <t>sh601665</t>
-  </si>
-  <si>
-    <t>sz300767</t>
-  </si>
-  <si>
-    <t>sh688660</t>
-  </si>
-  <si>
-    <t>sz300943</t>
-  </si>
-  <si>
-    <t>sh603160</t>
-  </si>
-  <si>
-    <t>sz300458</t>
-  </si>
-  <si>
-    <t>sz300829</t>
-  </si>
-  <si>
-    <t>sh600143</t>
-  </si>
-  <si>
-    <t>sh516160</t>
-  </si>
-  <si>
-    <t>sz300751</t>
-  </si>
-  <si>
-    <t>sh603799</t>
-  </si>
-  <si>
-    <t>sh688567</t>
-  </si>
-  <si>
-    <t>sz002074</t>
-  </si>
-  <si>
-    <t>sz002812</t>
-  </si>
-  <si>
-    <t>sz300198</t>
-  </si>
-  <si>
-    <t>sh688005</t>
-  </si>
-  <si>
-    <t>sh688063</t>
-  </si>
-  <si>
-    <t>sh515030</t>
-  </si>
-  <si>
-    <t>sz002127</t>
-  </si>
-  <si>
-    <t>sz002745</t>
-  </si>
-  <si>
-    <t>sh600336</t>
-  </si>
-  <si>
-    <t>sh600529</t>
-  </si>
-  <si>
-    <t>sh600009</t>
-  </si>
-  <si>
-    <t>sz300769</t>
-  </si>
-  <si>
-    <t>sz300001</t>
-  </si>
-  <si>
-    <t>sz002747</t>
-  </si>
-  <si>
-    <t>sz000066</t>
-  </si>
-  <si>
-    <t>sh600536</t>
-  </si>
-  <si>
-    <t>sh603002</t>
-  </si>
-  <si>
-    <t>sh600006</t>
-  </si>
-  <si>
-    <t>sh603239</t>
-  </si>
-  <si>
-    <t>sz002112</t>
-  </si>
-  <si>
-    <t>sh605008</t>
-  </si>
-  <si>
-    <t>sz002272</t>
-  </si>
-  <si>
-    <t>sh600563</t>
-  </si>
-  <si>
-    <t>sz002007</t>
-  </si>
-  <si>
-    <t>sh688169</t>
-  </si>
-  <si>
-    <t>sz300869</t>
-  </si>
-  <si>
-    <t>sh600497</t>
-  </si>
-  <si>
-    <t>sz300836</t>
-  </si>
-  <si>
-    <t>sz300529</t>
-  </si>
-  <si>
-    <t>sz002128</t>
-  </si>
-  <si>
-    <t>sz000831</t>
-  </si>
-  <si>
-    <t>sz300175</t>
-  </si>
-  <si>
-    <t>sz002239</t>
-  </si>
-  <si>
-    <t>sz300146</t>
-  </si>
-  <si>
-    <t>sh603881</t>
-  </si>
-  <si>
-    <t>sz300467</t>
-  </si>
-  <si>
-    <t>sz300212</t>
-  </si>
-  <si>
-    <t>sz300454</t>
-  </si>
-  <si>
-    <t>sz300083</t>
-  </si>
-  <si>
-    <t>sz002903</t>
-  </si>
-  <si>
-    <t>sz000980</t>
-  </si>
-  <si>
-    <t>sz300424</t>
-  </si>
-  <si>
-    <t>sh603316</t>
-  </si>
-  <si>
-    <t>sh603976</t>
-  </si>
-  <si>
-    <t>sz300674</t>
-  </si>
-  <si>
-    <t>sz002655</t>
-  </si>
-  <si>
-    <t>sh600053</t>
-  </si>
-  <si>
-    <t>sh601010</t>
-  </si>
-  <si>
-    <t>sh600963</t>
-  </si>
-  <si>
-    <t>sh601086</t>
-  </si>
-  <si>
-    <t>sz000782</t>
-  </si>
-  <si>
-    <t>sz300278</t>
-  </si>
-  <si>
-    <t>sh600550</t>
-  </si>
-  <si>
-    <t>sh600027</t>
-  </si>
-  <si>
-    <t>sz000791</t>
-  </si>
-  <si>
-    <t>sh601216</t>
-  </si>
-  <si>
-    <t>sz002049</t>
-  </si>
-  <si>
-    <t>sz002185</t>
-  </si>
-  <si>
-    <t>sz000009</t>
-  </si>
-  <si>
-    <t>sz000650</t>
-  </si>
-  <si>
-    <t>sh601669</t>
-  </si>
-  <si>
-    <t>sz002131</t>
-  </si>
-  <si>
-    <t>sh600268</t>
-  </si>
-  <si>
-    <t>sh600305</t>
-  </si>
-  <si>
-    <t>sz300710</t>
-  </si>
-  <si>
-    <t>sz002160</t>
-  </si>
-  <si>
-    <t>sz002183</t>
-  </si>
-  <si>
-    <t>sh600408</t>
-  </si>
-  <si>
-    <t>sh600757</t>
-  </si>
-  <si>
-    <t>sh600157</t>
-  </si>
-  <si>
-    <t>sz000723</t>
-  </si>
-  <si>
-    <t>sh601778</t>
-  </si>
-  <si>
-    <t>sh600477</t>
-  </si>
-  <si>
-    <t>sz002320</t>
-  </si>
-  <si>
-    <t>sz002169</t>
-  </si>
-  <si>
-    <t>sh605001</t>
-  </si>
-  <si>
-    <t>sz300450</t>
-  </si>
-  <si>
-    <t>sz300833</t>
-  </si>
-  <si>
-    <t>sz002660</t>
-  </si>
-  <si>
-    <t>sh603949</t>
-  </si>
-  <si>
-    <t>sz300832</t>
-  </si>
-  <si>
-    <t>sz002466</t>
-  </si>
-  <si>
-    <t>sh603706</t>
-  </si>
-  <si>
-    <t>sz000049</t>
-  </si>
-  <si>
-    <t>sh600198</t>
-  </si>
-  <si>
-    <t>sh600764</t>
-  </si>
-  <si>
-    <t>sh600148</t>
-  </si>
-  <si>
-    <t>sh601990</t>
-  </si>
-  <si>
-    <t>sh515050</t>
-  </si>
-  <si>
-    <t>sz300735</t>
-  </si>
-  <si>
-    <t>sh603197</t>
-  </si>
-  <si>
-    <t>sh600724</t>
-  </si>
-  <si>
-    <t>sz000661</t>
-  </si>
-  <si>
-    <t>sh600675</t>
-  </si>
-  <si>
-    <t>sz300601</t>
-  </si>
-  <si>
-    <t>sz300122</t>
-  </si>
-  <si>
-    <t>sz002237</t>
-  </si>
-  <si>
-    <t>sz300773</t>
-  </si>
-  <si>
-    <t>sz300496</t>
-  </si>
-  <si>
-    <t>sz300579</t>
-  </si>
-  <si>
-    <t>sz002163</t>
-  </si>
-  <si>
-    <t>sz300636</t>
-  </si>
-  <si>
-    <t>sz300051</t>
-  </si>
-  <si>
-    <t>sz002559</t>
-  </si>
-  <si>
-    <t>sz300024</t>
-  </si>
-  <si>
-    <t>sh603885</t>
-  </si>
-  <si>
-    <t>sh600875</t>
-  </si>
-  <si>
-    <t>sz000700</t>
-  </si>
-  <si>
-    <t>sh603005</t>
-  </si>
-  <si>
-    <t>sz002396</t>
-  </si>
-  <si>
-    <t>sz002369</t>
-  </si>
-  <si>
-    <t>sh600206</t>
-  </si>
-  <si>
-    <t>sz000810</t>
-  </si>
-  <si>
-    <t>sz300686</t>
-  </si>
-  <si>
-    <t>sz002943</t>
-  </si>
-  <si>
-    <t>sh603880</t>
-  </si>
-  <si>
-    <t>sh603989</t>
-  </si>
-  <si>
-    <t>sz300271</t>
-  </si>
-  <si>
-    <t>sz300469</t>
-  </si>
-  <si>
-    <t>sz300807</t>
-  </si>
-  <si>
-    <t>sz000156</t>
-  </si>
-  <si>
-    <t>sz002932</t>
-  </si>
-  <si>
-    <t>sz002530</t>
-  </si>
-  <si>
-    <t>sz300648</t>
-  </si>
-  <si>
-    <t>sz002326</t>
-  </si>
-  <si>
-    <t>sh603456</t>
-  </si>
-  <si>
-    <t>sz000078</t>
-  </si>
-  <si>
-    <t>sz000799</t>
-  </si>
-  <si>
-    <t>sz002940</t>
-  </si>
-  <si>
-    <t>sh600789</t>
-  </si>
-  <si>
-    <t>sz002430</t>
-  </si>
-  <si>
-    <t>sz300747</t>
-  </si>
-  <si>
-    <t>sz300569</t>
-  </si>
-  <si>
-    <t>sh600435</t>
-  </si>
-  <si>
-    <t>sh600098</t>
-  </si>
-  <si>
-    <t>sz300149</t>
-  </si>
-  <si>
-    <t>sz002497</t>
-  </si>
-  <si>
-    <t>sz300407</t>
-  </si>
-  <si>
-    <t>sh603888</t>
-  </si>
-  <si>
-    <t>sz300339</t>
-  </si>
-  <si>
-    <t>sh512480</t>
-  </si>
-  <si>
-    <t>sz300343</t>
-  </si>
-  <si>
-    <t>sz000410</t>
-  </si>
-  <si>
-    <t>sh600588</t>
-  </si>
-  <si>
-    <t>sz002795</t>
-  </si>
-  <si>
-    <t>sz300055</t>
-  </si>
-  <si>
-    <t>sh600702</t>
-  </si>
-  <si>
-    <t>sz002600</t>
-  </si>
-  <si>
-    <t>sh600548</t>
-  </si>
-  <si>
-    <t>sz002669</t>
-  </si>
-  <si>
-    <t>sh603260</t>
-  </si>
-  <si>
-    <t>sz002294</t>
-  </si>
-  <si>
-    <t>sh600748</t>
-  </si>
-  <si>
-    <t>sz002343</t>
-  </si>
-  <si>
-    <t>sz300221</t>
-  </si>
-  <si>
-    <t>sh600489</t>
-  </si>
-  <si>
-    <t>sh600338</t>
-  </si>
-  <si>
-    <t>sh603063</t>
-  </si>
-  <si>
-    <t>sz300020</t>
-  </si>
-  <si>
-    <t>sh603717</t>
-  </si>
-  <si>
-    <t>sz002458</t>
-  </si>
-  <si>
-    <t>sz300796</t>
-  </si>
-  <si>
-    <t>sz002959</t>
-  </si>
-  <si>
-    <t>sz000029</t>
-  </si>
-  <si>
-    <t>sz000011</t>
-  </si>
-  <si>
-    <t>sz000021</t>
-  </si>
-  <si>
-    <t>sh601916</t>
-  </si>
-  <si>
-    <t>sh600988</t>
-  </si>
-  <si>
-    <t>sh600903</t>
-  </si>
-  <si>
-    <t>sz000529</t>
-  </si>
-  <si>
-    <t>sh601975</t>
-  </si>
-  <si>
-    <t>sz000513</t>
-  </si>
-  <si>
-    <t>sz002909</t>
-  </si>
-  <si>
-    <t>sh601155</t>
-  </si>
-  <si>
-    <t>sz300471</t>
-  </si>
-  <si>
-    <t>sh600283</t>
-  </si>
-  <si>
-    <t>sh601608</t>
-  </si>
-  <si>
-    <t>sz002190</t>
-  </si>
-  <si>
-    <t>sh600177</t>
-  </si>
-  <si>
-    <t>sz300741</t>
-  </si>
-  <si>
-    <t>sz002292</t>
-  </si>
-  <si>
-    <t>sh600235</t>
-  </si>
-  <si>
-    <t>sh600089</t>
-  </si>
-  <si>
-    <t>sz300711</t>
-  </si>
-  <si>
-    <t>sh603602</t>
-  </si>
-  <si>
-    <t>sh600280</t>
-  </si>
-  <si>
-    <t>sh600622</t>
-  </si>
-  <si>
-    <t>sh603010</t>
-  </si>
-  <si>
-    <t>sz300506</t>
-  </si>
-  <si>
-    <t>sz002236</t>
-  </si>
-  <si>
-    <t>sz300525</t>
-  </si>
-  <si>
-    <t>sz002908</t>
-  </si>
-  <si>
-    <t>sz300180</t>
-  </si>
-  <si>
-    <t>sh600754</t>
-  </si>
-  <si>
-    <t>sz002821</t>
-  </si>
-  <si>
-    <t>sh600271</t>
-  </si>
-  <si>
-    <t>sh600984</t>
-  </si>
-  <si>
-    <t>sh601021</t>
-  </si>
-  <si>
-    <t>sh600584</t>
-  </si>
-  <si>
-    <t>sh601139</t>
-  </si>
-  <si>
-    <t>sz002629</t>
-  </si>
-  <si>
-    <t>sz159949</t>
-  </si>
-  <si>
-    <t>sh603790</t>
-  </si>
-  <si>
-    <t>sz002936</t>
-  </si>
-  <si>
-    <t>sh603810</t>
-  </si>
-  <si>
-    <t>sz000735</t>
-  </si>
-  <si>
-    <t>sz300017</t>
-  </si>
-  <si>
-    <t>sz000025</t>
-  </si>
-  <si>
-    <t>sz300664</t>
-  </si>
-  <si>
-    <t>sh600340</t>
-  </si>
-  <si>
-    <t>sh600037</t>
-  </si>
-  <si>
-    <t>sz000932</t>
-  </si>
-  <si>
-    <t>sh603058</t>
-  </si>
-  <si>
-    <t>sh600729</t>
-  </si>
-  <si>
-    <t>sz300676</t>
-  </si>
-  <si>
-    <t>sh601108</t>
-  </si>
-  <si>
-    <t>sh601933</t>
-  </si>
-  <si>
-    <t>sh603661</t>
-  </si>
-  <si>
-    <t>sh603969</t>
-  </si>
-  <si>
-    <t>sh600135</t>
-  </si>
-  <si>
-    <t>sz000839</t>
-  </si>
-  <si>
-    <t>sz002843</t>
-  </si>
-  <si>
-    <t>sz002545</t>
-  </si>
-  <si>
-    <t>sz002460</t>
-  </si>
-  <si>
-    <t>sz002218</t>
-  </si>
-  <si>
-    <t>sz002347</t>
-  </si>
-  <si>
-    <t>sz002549</t>
-  </si>
-  <si>
-    <t>sh601369</t>
-  </si>
-  <si>
-    <t>sz300285</t>
-  </si>
-  <si>
-    <t>sz002167</t>
-  </si>
-  <si>
-    <t>sz300008</t>
-  </si>
-  <si>
-    <t>sz300397</t>
-  </si>
-  <si>
-    <t>sz300682</t>
-  </si>
-  <si>
-    <t>sh600871</t>
-  </si>
-  <si>
-    <t>sz000628</t>
-  </si>
-  <si>
-    <t>sz000526</t>
-  </si>
-  <si>
-    <t>sh603667</t>
-  </si>
-  <si>
-    <t>sh603025</t>
-  </si>
-  <si>
-    <t>sz002673</t>
-  </si>
-  <si>
-    <t>sh601198</t>
-  </si>
-  <si>
-    <t>sz002291</t>
-  </si>
-  <si>
-    <t>sz000555</t>
-  </si>
-  <si>
-    <t>sh600153</t>
-  </si>
-  <si>
-    <t>sh600058</t>
-  </si>
-  <si>
-    <t>sz002654</t>
-  </si>
-  <si>
-    <t>sh600119</t>
-  </si>
-  <si>
-    <t>sz002067</t>
-  </si>
-  <si>
-    <t>sz002358</t>
-  </si>
-  <si>
-    <t>sz002276</t>
-  </si>
-  <si>
-    <t>sz002043</t>
-  </si>
-  <si>
-    <t>sz002445</t>
-  </si>
-  <si>
-    <t>sz002081</t>
-  </si>
-  <si>
-    <t>sh600797</t>
-  </si>
-  <si>
-    <t>sz002328</t>
-  </si>
-  <si>
-    <t>sz002223</t>
-  </si>
-  <si>
-    <t>sz002601</t>
-  </si>
-  <si>
-    <t>sz002573</t>
-  </si>
-  <si>
-    <t>sz000816</t>
-  </si>
-  <si>
-    <t>sz002104</t>
-  </si>
-  <si>
-    <t>sh600558</t>
-  </si>
-  <si>
-    <t>sh601566</t>
-  </si>
-  <si>
-    <t>sh601106</t>
-  </si>
-  <si>
-    <t>sz002095</t>
-  </si>
-  <si>
-    <t>sz002130</t>
-  </si>
-  <si>
-    <t>sz001914</t>
-  </si>
-  <si>
-    <t>sz002306</t>
-  </si>
-  <si>
-    <t>sh600756</t>
-  </si>
-  <si>
-    <t>sh600176</t>
-  </si>
-  <si>
-    <t>sz300061</t>
-  </si>
-  <si>
-    <t>sh600829</t>
-  </si>
-  <si>
-    <t>sz002448</t>
-  </si>
-  <si>
-    <t>sh601000</t>
-  </si>
-  <si>
-    <t>sh600055</t>
-  </si>
-  <si>
-    <t>sz300084</t>
-  </si>
-  <si>
-    <t>sz002353</t>
-  </si>
-  <si>
-    <t>sz002086</t>
-  </si>
-  <si>
-    <t>sh601890</t>
-  </si>
-  <si>
-    <t>sz000039</t>
-  </si>
-  <si>
-    <t>sh601028</t>
-  </si>
-  <si>
-    <t>sh603030</t>
-  </si>
-  <si>
-    <t>sz000905</t>
-  </si>
-  <si>
-    <t>sz002153</t>
-  </si>
-  <si>
-    <t>sz399001</t>
-  </si>
-  <si>
-    <t>sh600712</t>
-  </si>
-  <si>
-    <t>sz301287</t>
-  </si>
-  <si>
-    <t>sz300963</t>
-  </si>
-  <si>
-    <t>sz300316</t>
-  </si>
-  <si>
-    <t>sz002572</t>
-  </si>
-  <si>
-    <t>sz300677</t>
-  </si>
-  <si>
-    <t>sz000596</t>
-  </si>
-  <si>
-    <t>sh603816</t>
-  </si>
-  <si>
-    <t>sz000568</t>
-  </si>
-  <si>
-    <t>sh600546</t>
-  </si>
-  <si>
-    <t>sz300596</t>
-  </si>
-  <si>
-    <t>sz002555</t>
-  </si>
-  <si>
-    <t>sh600507</t>
-  </si>
-  <si>
-    <t>sh600132</t>
-  </si>
-  <si>
-    <t>sz002648</t>
-  </si>
-  <si>
-    <t>sz002035</t>
-  </si>
-  <si>
-    <t>sz000858</t>
-  </si>
-  <si>
-    <t>sz300628</t>
-  </si>
-  <si>
-    <t>sz002120</t>
-  </si>
-  <si>
-    <t>sh600872</t>
-  </si>
-  <si>
-    <t>sz002233</t>
-  </si>
-  <si>
-    <t>sz300705</t>
-  </si>
-  <si>
-    <t>sh600976</t>
-  </si>
-  <si>
-    <t>sh601877</t>
-  </si>
-  <si>
-    <t>sh600522</t>
-  </si>
-  <si>
-    <t>sz000821</t>
-  </si>
-  <si>
-    <t>sz000739</t>
-  </si>
-  <si>
-    <t>sh600587</t>
-  </si>
-  <si>
-    <t>sh900925</t>
   </si>
 </sst>
 </file>
@@ -2038,13 +2023,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2329,11 +2307,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:A443"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:A437"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="9.81818181818182" style="1"/>
+    <col min="1" max="1" width="9.81730769230769" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
@@ -2341,2217 +2319,2199 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" hidden="1" spans="1:1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" hidden="1" spans="1:1">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" hidden="1" spans="1:1">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" hidden="1" spans="1:1">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" hidden="1" spans="1:1">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" hidden="1" spans="1:1">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" hidden="1" spans="1:1">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" hidden="1" spans="1:1">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" hidden="1" spans="1:1">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" hidden="1" spans="1:1">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" hidden="1" spans="1:1">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" hidden="1" spans="1:1">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" hidden="1" spans="1:1">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" hidden="1" spans="1:1">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="1" t="s">
+    <row r="16" hidden="1" spans="1:1">
+      <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" hidden="1" spans="1:1">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" hidden="1" spans="1:1">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" hidden="1" spans="1:1">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" hidden="1" spans="1:1">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" hidden="1" spans="1:1">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" hidden="1" spans="1:1">
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" hidden="1" spans="1:1">
       <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" hidden="1" spans="1:1">
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" hidden="1" spans="1:1">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" hidden="1" spans="1:1">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" hidden="1" spans="1:1">
       <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" hidden="1" spans="1:1">
       <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" hidden="1" spans="1:1">
       <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" hidden="1" spans="1:1">
       <c r="A30" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" hidden="1" spans="1:1">
       <c r="A31" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" hidden="1" spans="1:1">
       <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" hidden="1" spans="1:1">
       <c r="A33" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" hidden="1" spans="1:1">
       <c r="A34" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" hidden="1" spans="1:1">
       <c r="A35" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" hidden="1" spans="1:1">
       <c r="A36" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" hidden="1" spans="1:1">
       <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" hidden="1" spans="1:1">
       <c r="A38" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" hidden="1" spans="1:1">
       <c r="A39" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" hidden="1" spans="1:1">
       <c r="A40" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" hidden="1" spans="1:1">
       <c r="A41" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" hidden="1" spans="1:1">
       <c r="A42" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" hidden="1" spans="1:1">
       <c r="A43" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" hidden="1" spans="1:1">
       <c r="A44" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
+    <row r="45" hidden="1" spans="1:1">
+      <c r="A45" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" hidden="1" spans="1:1">
       <c r="A46" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
-      <c r="A47" s="1" t="s">
+    <row r="47" hidden="1" spans="1:1">
+      <c r="A47" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" hidden="1" spans="1:1">
       <c r="A48" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" hidden="1" spans="1:1">
       <c r="A49" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
+    <row r="50" hidden="1" spans="1:1">
       <c r="A50" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="1" t="s">
+    <row r="51" hidden="1" spans="1:1">
+      <c r="A51" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
+    <row r="52" hidden="1" spans="1:1">
       <c r="A52" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
+    <row r="53" hidden="1" spans="1:1">
       <c r="A53" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54" hidden="1" spans="1:1">
       <c r="A54" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55" hidden="1" spans="1:1">
       <c r="A55" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" hidden="1" spans="1:1">
       <c r="A56" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" hidden="1" spans="1:1">
       <c r="A57" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="1" t="s">
+    <row r="58" hidden="1" spans="1:1">
+      <c r="A58" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" hidden="1" spans="1:1">
       <c r="A59" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" hidden="1" spans="1:1">
       <c r="A60" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" hidden="1" spans="1:1">
       <c r="A61" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
+    <row r="62" hidden="1" spans="1:1">
       <c r="A62" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
+    <row r="63" hidden="1" spans="1:1">
       <c r="A63" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64" hidden="1" spans="1:1">
       <c r="A64" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:1">
+    <row r="65" hidden="1" spans="1:1">
       <c r="A65" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:1">
+    <row r="66" hidden="1" spans="1:1">
       <c r="A66" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
+    <row r="67" hidden="1" spans="1:1">
       <c r="A67" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
+    <row r="68" hidden="1" spans="1:1">
       <c r="A68" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:1">
+    <row r="69" hidden="1" spans="1:1">
       <c r="A69" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
+    <row r="70" hidden="1" spans="1:1">
       <c r="A70" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:1">
+    <row r="71" hidden="1" spans="1:1">
       <c r="A71" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:1">
+    <row r="72" hidden="1" spans="1:1">
       <c r="A72" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:1">
+    <row r="73" hidden="1" spans="1:1">
       <c r="A73" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="1:1">
+    <row r="74" hidden="1" spans="1:1">
       <c r="A74" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:1">
+    <row r="75" hidden="1" spans="1:1">
       <c r="A75" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:1">
+    <row r="76" hidden="1" spans="1:1">
       <c r="A76" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:1">
+    <row r="77" hidden="1" spans="1:1">
       <c r="A77" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:1">
+    <row r="78" hidden="1" spans="1:1">
       <c r="A78" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:1">
+    <row r="79" hidden="1" spans="1:1">
       <c r="A79" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:1">
+    <row r="80" hidden="1" spans="1:1">
       <c r="A80" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="1:1">
+    <row r="81" hidden="1" spans="1:1">
       <c r="A81" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="1:1">
-      <c r="A82" s="1" t="s">
+    <row r="82" hidden="1" spans="1:1">
+      <c r="A82" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:1">
+    <row r="83" hidden="1" spans="1:1">
       <c r="A83" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="84" spans="1:1">
+    <row r="84" hidden="1" spans="1:1">
       <c r="A84" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:1">
+    <row r="85" hidden="1" spans="1:1">
       <c r="A85" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:1">
+    <row r="86" hidden="1" spans="1:1">
       <c r="A86" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="1:1">
-      <c r="A87" s="1" t="s">
+    <row r="87" hidden="1" spans="1:1">
+      <c r="A87" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:1">
+    <row r="88" hidden="1" spans="1:1">
       <c r="A88" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="89" spans="1:1">
+    <row r="89" hidden="1" spans="1:1">
       <c r="A89" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:1">
+    <row r="90" hidden="1" spans="1:1">
       <c r="A90" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:1">
+    <row r="91" hidden="1" spans="1:1">
       <c r="A91" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:1">
+    <row r="92" hidden="1" spans="1:1">
       <c r="A92" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="1:1">
+    <row r="93" hidden="1" spans="1:1">
       <c r="A93" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="94" spans="1:1">
+    <row r="94" hidden="1" spans="1:1">
       <c r="A94" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:1">
+    <row r="95" hidden="1" spans="1:1">
       <c r="A95" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="1:1">
+    <row r="96" hidden="1" spans="1:1">
       <c r="A96" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="97" spans="1:1">
+    <row r="97" hidden="1" spans="1:1">
       <c r="A97" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="1:1">
+    <row r="98" hidden="1" spans="1:1">
       <c r="A98" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="1:1">
+    <row r="99" hidden="1" spans="1:1">
       <c r="A99" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:1">
+    <row r="100" hidden="1" spans="1:1">
       <c r="A100" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="101" spans="1:1">
+    <row r="101" hidden="1" spans="1:1">
       <c r="A101" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:1">
+    <row r="102" hidden="1" spans="1:1">
       <c r="A102" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="1:1">
+    <row r="103" hidden="1" spans="1:1">
       <c r="A103" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="104" spans="1:1">
+    <row r="104" hidden="1" spans="1:1">
       <c r="A104" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="105" spans="1:1">
+    <row r="105" hidden="1" spans="1:1">
       <c r="A105" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="106" spans="1:1">
+    <row r="106" hidden="1" spans="1:1">
       <c r="A106" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="107" spans="1:1">
+    <row r="107" hidden="1" spans="1:1">
       <c r="A107" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="108" spans="1:1">
+    <row r="108" hidden="1" spans="1:1">
       <c r="A108" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="1:1">
+    <row r="109" hidden="1" spans="1:1">
       <c r="A109" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="1:1">
+    <row r="110" hidden="1" spans="1:1">
       <c r="A110" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="111" spans="1:1">
-      <c r="A111" s="1" t="s">
+    <row r="111" hidden="1" spans="1:1">
+      <c r="A111" s="2" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="112" spans="1:1">
+    <row r="112" hidden="1" spans="1:1">
       <c r="A112" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="113" spans="1:1">
+    <row r="113" hidden="1" spans="1:1">
       <c r="A113" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="114" spans="1:1">
+    <row r="114" hidden="1" spans="1:1">
       <c r="A114" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="115" spans="1:1">
+    <row r="115" hidden="1" spans="1:1">
       <c r="A115" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="116" spans="1:1">
+    <row r="116" hidden="1" spans="1:1">
       <c r="A116" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="117" spans="1:1">
+    <row r="117" hidden="1" spans="1:1">
       <c r="A117" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="118" spans="1:1">
+    <row r="118" hidden="1" spans="1:1">
       <c r="A118" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="119" spans="1:1">
+    <row r="119" hidden="1" spans="1:1">
       <c r="A119" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="120" spans="1:1">
+    <row r="120" hidden="1" spans="1:1">
       <c r="A120" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="121" spans="1:1">
+    <row r="121" hidden="1" spans="1:1">
       <c r="A121" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="1:1">
+    <row r="122" hidden="1" spans="1:1">
       <c r="A122" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:1">
+    <row r="123" hidden="1" spans="1:1">
       <c r="A123" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="124" spans="1:1">
+    <row r="124" hidden="1" spans="1:1">
       <c r="A124" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="1:1">
+    <row r="125" hidden="1" spans="1:1">
       <c r="A125" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:1">
+    <row r="126" hidden="1" spans="1:1">
       <c r="A126" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:1">
+    <row r="127" hidden="1" spans="1:1">
       <c r="A127" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="128" spans="1:1">
+    <row r="128" hidden="1" spans="1:1">
       <c r="A128" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="129" spans="1:1">
+    <row r="129" hidden="1" spans="1:1">
       <c r="A129" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="130" spans="1:1">
+    <row r="130" hidden="1" spans="1:1">
       <c r="A130" s="1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="131" spans="1:1">
+    <row r="131" hidden="1" spans="1:1">
       <c r="A131" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="132" spans="1:1">
+    <row r="132" hidden="1" spans="1:1">
       <c r="A132" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="133" spans="1:1">
+    <row r="133" hidden="1" spans="1:1">
       <c r="A133" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="134" spans="1:1">
+    <row r="134" hidden="1" spans="1:1">
       <c r="A134" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="135" spans="1:1">
+    <row r="135" hidden="1" spans="1:1">
       <c r="A135" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="136" spans="1:1">
+    <row r="136" hidden="1" spans="1:1">
       <c r="A136" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="137" spans="1:1">
+    <row r="137" hidden="1" spans="1:1">
       <c r="A137" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="138" spans="1:1">
+    <row r="138" hidden="1" spans="1:1">
       <c r="A138" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="139" spans="1:1">
+    <row r="139" hidden="1" spans="1:1">
       <c r="A139" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:1">
+    <row r="140" hidden="1" spans="1:1">
       <c r="A140" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="141" spans="1:1">
+    <row r="141" hidden="1" spans="1:1">
       <c r="A141" s="1" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="142" spans="1:1">
+    <row r="142" hidden="1" spans="1:1">
       <c r="A142" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="143" spans="1:1">
+    <row r="143" hidden="1" spans="1:1">
       <c r="A143" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="144" spans="1:1">
+    <row r="144" hidden="1" spans="1:1">
       <c r="A144" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="145" spans="1:1">
+    <row r="145" hidden="1" spans="1:1">
       <c r="A145" s="1" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="146" spans="1:1">
+    <row r="146" hidden="1" spans="1:1">
       <c r="A146" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="147" spans="1:1">
-      <c r="A147" s="1" t="s">
+    <row r="147" hidden="1" spans="1:1">
+      <c r="A147" s="2" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="148" spans="1:1">
+    <row r="148" hidden="1" spans="1:1">
       <c r="A148" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="149" spans="1:1">
+    <row r="149" hidden="1" spans="1:1">
       <c r="A149" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="150" spans="1:1">
+    <row r="150" hidden="1" spans="1:1">
       <c r="A150" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="151" spans="1:1">
+    <row r="151" hidden="1" spans="1:1">
       <c r="A151" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="152" spans="1:1">
+    <row r="152" hidden="1" spans="1:1">
       <c r="A152" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="153" spans="1:1">
+    <row r="153" hidden="1" spans="1:1">
       <c r="A153" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="154" spans="1:1">
+    <row r="154" hidden="1" spans="1:1">
       <c r="A154" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="155" spans="1:1">
+    <row r="155" hidden="1" spans="1:1">
       <c r="A155" s="1" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="156" spans="1:1">
+    <row r="156" hidden="1" spans="1:1">
       <c r="A156" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="157" spans="1:1">
+    <row r="157" hidden="1" spans="1:1">
       <c r="A157" s="1" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="158" spans="1:1">
+    <row r="158" hidden="1" spans="1:1">
       <c r="A158" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="159" spans="1:1">
+    <row r="159" hidden="1" spans="1:1">
       <c r="A159" s="1" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="160" spans="1:1">
+    <row r="160" hidden="1" spans="1:1">
       <c r="A160" s="1" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="161" spans="1:1">
+    <row r="161" hidden="1" spans="1:1">
       <c r="A161" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="162" spans="1:1">
+    <row r="162" hidden="1" spans="1:1">
       <c r="A162" s="1" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="163" spans="1:1">
+    <row r="163" hidden="1" spans="1:1">
       <c r="A163" s="1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="164" spans="1:1">
+    <row r="164" hidden="1" spans="1:1">
       <c r="A164" s="1" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="165" spans="1:1">
+    <row r="165" hidden="1" spans="1:1">
       <c r="A165" s="1" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="166" spans="1:1">
+    <row r="166" hidden="1" spans="1:1">
       <c r="A166" s="1" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="167" spans="1:1">
+    <row r="167" hidden="1" spans="1:1">
       <c r="A167" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="168" spans="1:1">
+    <row r="168" hidden="1" spans="1:1">
       <c r="A168" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="169" spans="1:1">
+    <row r="169" hidden="1" spans="1:1">
       <c r="A169" s="1" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="170" spans="1:1">
+    <row r="170" hidden="1" spans="1:1">
       <c r="A170" s="1" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="171" spans="1:1">
+    <row r="171" hidden="1" spans="1:1">
       <c r="A171" s="1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="172" spans="1:1">
+    <row r="172" hidden="1" spans="1:1">
       <c r="A172" s="1" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="173" spans="1:1">
+    <row r="173" hidden="1" spans="1:1">
       <c r="A173" s="1" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="174" spans="1:1">
+    <row r="174" hidden="1" spans="1:1">
       <c r="A174" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="175" spans="1:1">
+    <row r="175" hidden="1" spans="1:1">
       <c r="A175" s="1" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="176" spans="1:1">
+    <row r="176" hidden="1" spans="1:1">
       <c r="A176" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="177" spans="1:1">
+    <row r="177" hidden="1" spans="1:1">
       <c r="A177" s="1" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="178" spans="1:1">
+    <row r="178" hidden="1" spans="1:1">
       <c r="A178" s="1" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="179" spans="1:1">
-      <c r="A179" s="1" t="s">
+    <row r="179" hidden="1" spans="1:1">
+      <c r="A179" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="180" spans="1:1">
+    <row r="180" hidden="1" spans="1:1">
       <c r="A180" s="1" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="181" spans="1:1">
+    <row r="181" hidden="1" spans="1:1">
       <c r="A181" s="1" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="182" spans="1:1">
+    <row r="182" hidden="1" spans="1:1">
       <c r="A182" s="1" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="183" spans="1:1">
+    <row r="183" hidden="1" spans="1:1">
       <c r="A183" s="1" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="184" spans="1:1">
+    <row r="184" hidden="1" spans="1:1">
       <c r="A184" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="185" spans="1:1">
+    <row r="185" hidden="1" spans="1:1">
       <c r="A185" s="1" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="186" spans="1:1">
+    <row r="186" hidden="1" spans="1:1">
       <c r="A186" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="187" spans="1:1">
+    <row r="187" hidden="1" spans="1:1">
       <c r="A187" s="1" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="188" spans="1:1">
+    <row r="188" hidden="1" spans="1:1">
       <c r="A188" s="1" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="189" spans="1:1">
+    <row r="189" hidden="1" spans="1:1">
       <c r="A189" s="1" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="190" spans="1:1">
+    <row r="190" hidden="1" spans="1:1">
       <c r="A190" s="1" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="191" spans="1:1">
+    <row r="191" hidden="1" spans="1:1">
       <c r="A191" s="1" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="192" spans="1:1">
+    <row r="192" hidden="1" spans="1:1">
       <c r="A192" s="1" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="193" spans="1:1">
+    <row r="193" hidden="1" spans="1:1">
       <c r="A193" s="1" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="194" spans="1:1">
+    <row r="194" hidden="1" spans="1:1">
       <c r="A194" s="1" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="195" spans="1:1">
+    <row r="195" hidden="1" spans="1:1">
       <c r="A195" s="1" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="196" spans="1:1">
+    <row r="196" hidden="1" spans="1:1">
       <c r="A196" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="197" spans="1:1">
-      <c r="A197" s="1" t="s">
+    <row r="197" hidden="1" spans="1:1">
+      <c r="A197" s="2" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="198" spans="1:1">
-      <c r="A198" s="1" t="s">
+    <row r="198" hidden="1" spans="1:1">
+      <c r="A198" s="2" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="199" spans="1:1">
+    <row r="199" hidden="1" spans="1:1">
       <c r="A199" s="1" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="200" spans="1:1">
+    <row r="200" hidden="1" spans="1:1">
       <c r="A200" s="1" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="201" spans="1:1">
+    <row r="201" hidden="1" spans="1:1">
       <c r="A201" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="202" spans="1:1">
+    <row r="202" hidden="1" spans="1:1">
       <c r="A202" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="203" spans="1:1">
+    <row r="203" hidden="1" spans="1:1">
       <c r="A203" s="1" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="204" spans="1:1">
+    <row r="204" hidden="1" spans="1:1">
       <c r="A204" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="205" spans="1:1">
+    <row r="205" hidden="1" spans="1:1">
       <c r="A205" s="1" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="206" spans="1:1">
+    <row r="206" hidden="1" spans="1:1">
       <c r="A206" s="1" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="207" spans="1:1">
+    <row r="207" hidden="1" spans="1:1">
       <c r="A207" s="1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="208" spans="1:1">
-      <c r="A208" s="1" t="s">
+    <row r="208" hidden="1" spans="1:1">
+      <c r="A208" s="2" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="209" spans="1:1">
+    <row r="209" hidden="1" spans="1:1">
       <c r="A209" s="1" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="210" spans="1:1">
+    <row r="210" hidden="1" spans="1:1">
       <c r="A210" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="211" spans="1:1">
+    <row r="211" hidden="1" spans="1:1">
       <c r="A211" s="1" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="212" spans="1:1">
+    <row r="212" hidden="1" spans="1:1">
       <c r="A212" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="213" spans="1:1">
+    <row r="213" hidden="1" spans="1:1">
       <c r="A213" s="1" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="214" spans="1:1">
+    <row r="214" hidden="1" spans="1:1">
       <c r="A214" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="215" spans="1:1">
-      <c r="A215" s="1" t="s">
+    <row r="215" hidden="1" spans="1:1">
+      <c r="A215" s="2" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="216" spans="1:1">
+    <row r="216" hidden="1" spans="1:1">
       <c r="A216" s="1" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="217" spans="1:1">
+    <row r="217" hidden="1" spans="1:1">
       <c r="A217" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="218" spans="1:1">
-      <c r="A218" s="1" t="s">
+    <row r="218" hidden="1" spans="1:1">
+      <c r="A218" s="2" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="219" spans="1:1">
+    <row r="219" hidden="1" spans="1:1">
       <c r="A219" s="1" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="220" spans="1:1">
+    <row r="220" hidden="1" spans="1:1">
       <c r="A220" s="1" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="221" spans="1:1">
+    <row r="221" hidden="1" spans="1:1">
       <c r="A221" s="1" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="222" spans="1:1">
+    <row r="222" hidden="1" spans="1:1">
       <c r="A222" s="1" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="223" spans="1:1">
+    <row r="223" hidden="1" spans="1:1">
       <c r="A223" s="1" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="224" spans="1:1">
+    <row r="224" hidden="1" spans="1:1">
       <c r="A224" s="1" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="225" spans="1:1">
+    <row r="225" hidden="1" spans="1:1">
       <c r="A225" s="1" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="226" spans="1:1">
+    <row r="226" hidden="1" spans="1:1">
       <c r="A226" s="1" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="227" spans="1:1">
+    <row r="227" hidden="1" spans="1:1">
       <c r="A227" s="1" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="228" spans="1:1">
+    <row r="228" hidden="1" spans="1:1">
       <c r="A228" s="1" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="229" spans="1:1">
+    <row r="229" hidden="1" spans="1:1">
       <c r="A229" s="1" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="230" spans="1:1">
+    <row r="230" hidden="1" spans="1:1">
       <c r="A230" s="1" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="231" spans="1:1">
+    <row r="231" hidden="1" spans="1:1">
       <c r="A231" s="1" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="232" spans="1:1">
+    <row r="232" hidden="1" spans="1:1">
       <c r="A232" s="1" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="233" spans="1:1">
-      <c r="A233" s="1" t="s">
+    <row r="233" hidden="1" spans="1:1">
+      <c r="A233" s="2" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="234" spans="1:1">
+    <row r="234" hidden="1" spans="1:1">
       <c r="A234" s="1" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="235" spans="1:1">
+    <row r="235" hidden="1" spans="1:1">
       <c r="A235" s="1" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="236" spans="1:1">
+    <row r="236" hidden="1" spans="1:1">
       <c r="A236" s="1" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="237" spans="1:1">
+    <row r="237" hidden="1" spans="1:1">
       <c r="A237" s="1" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="238" spans="1:1">
+    <row r="238" hidden="1" spans="1:1">
       <c r="A238" s="1" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="239" spans="1:1">
+    <row r="239" hidden="1" spans="1:1">
       <c r="A239" s="1" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="240" spans="1:1">
+    <row r="240" hidden="1" spans="1:1">
       <c r="A240" s="1" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="241" spans="1:1">
+    <row r="241" hidden="1" spans="1:1">
       <c r="A241" s="1" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="242" spans="1:1">
+    <row r="242" hidden="1" spans="1:1">
       <c r="A242" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="243" spans="1:1">
+    <row r="243" hidden="1" spans="1:1">
       <c r="A243" s="1" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="244" spans="1:1">
-      <c r="A244" s="1" t="s">
+    <row r="244" hidden="1" spans="1:1">
+      <c r="A244" s="2" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="245" spans="1:1">
+    <row r="245" hidden="1" spans="1:1">
       <c r="A245" s="1" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="246" spans="1:1">
+    <row r="246" hidden="1" spans="1:1">
       <c r="A246" s="1" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="247" spans="1:1">
+    <row r="247" hidden="1" spans="1:1">
       <c r="A247" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="248" spans="1:1">
+    <row r="248" hidden="1" spans="1:1">
       <c r="A248" s="1" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="249" spans="1:1">
+    <row r="249" hidden="1" spans="1:1">
       <c r="A249" s="1" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="250" spans="1:1">
+    <row r="250" hidden="1" spans="1:1">
       <c r="A250" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="251" spans="1:1">
+    <row r="251" hidden="1" spans="1:1">
       <c r="A251" s="1" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="252" spans="1:1">
+    <row r="252" hidden="1" spans="1:1">
       <c r="A252" s="1" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="253" spans="1:1">
+    <row r="253" hidden="1" spans="1:1">
       <c r="A253" s="1" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="254" spans="1:1">
+    <row r="254" hidden="1" spans="1:1">
       <c r="A254" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="255" spans="1:1">
+    <row r="255" hidden="1" spans="1:1">
       <c r="A255" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="256" spans="1:1">
+    <row r="256" hidden="1" spans="1:1">
       <c r="A256" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="257" spans="1:1">
+    <row r="257" hidden="1" spans="1:1">
       <c r="A257" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="258" spans="1:1">
+    <row r="258" hidden="1" spans="1:1">
       <c r="A258" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="259" spans="1:1">
+    <row r="259" hidden="1" spans="1:1">
       <c r="A259" s="1" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="260" spans="1:1">
+    <row r="260" hidden="1" spans="1:1">
       <c r="A260" s="1" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="261" spans="1:1">
-      <c r="A261" s="1" t="s">
+    <row r="261" hidden="1" spans="1:1">
+      <c r="A261" s="2" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="262" spans="1:1">
+    <row r="262" hidden="1" spans="1:1">
       <c r="A262" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="263" spans="1:1">
+    <row r="263" hidden="1" spans="1:1">
       <c r="A263" s="1" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="264" spans="1:1">
+    <row r="264" hidden="1" spans="1:1">
       <c r="A264" s="1" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="265" spans="1:1">
+    <row r="265" hidden="1" spans="1:1">
       <c r="A265" s="1" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="266" spans="1:1">
+    <row r="266" hidden="1" spans="1:1">
       <c r="A266" s="1" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="267" spans="1:1">
+    <row r="267" hidden="1" spans="1:1">
       <c r="A267" s="1" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="268" spans="1:1">
+    <row r="268" hidden="1" spans="1:1">
       <c r="A268" s="1" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="269" spans="1:1">
+    <row r="269" hidden="1" spans="1:1">
       <c r="A269" s="1" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="270" spans="1:1">
+    <row r="270" hidden="1" spans="1:1">
       <c r="A270" s="1" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="271" spans="1:1">
+    <row r="271" hidden="1" spans="1:1">
       <c r="A271" s="1" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="272" spans="1:1">
+    <row r="272" hidden="1" spans="1:1">
       <c r="A272" s="1" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="273" spans="1:1">
+    <row r="273" hidden="1" spans="1:1">
       <c r="A273" s="1" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="274" spans="1:1">
+    <row r="274" hidden="1" spans="1:1">
       <c r="A274" s="1" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="275" spans="1:1">
+    <row r="275" hidden="1" spans="1:1">
       <c r="A275" s="1" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="276" spans="1:1">
+    <row r="276" hidden="1" spans="1:1">
       <c r="A276" s="1" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="277" spans="1:1">
+    <row r="277" hidden="1" spans="1:1">
       <c r="A277" s="1" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="278" spans="1:1">
+    <row r="278" hidden="1" spans="1:1">
       <c r="A278" s="1" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="279" spans="1:1">
+    <row r="279" hidden="1" spans="1:1">
       <c r="A279" s="1" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="280" spans="1:1">
+    <row r="280" hidden="1" spans="1:1">
       <c r="A280" s="1" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="281" spans="1:1">
+    <row r="281" hidden="1" spans="1:1">
       <c r="A281" s="1" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="282" spans="1:1">
+    <row r="282" hidden="1" spans="1:1">
       <c r="A282" s="1" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="283" spans="1:1">
+    <row r="283" hidden="1" spans="1:1">
       <c r="A283" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="284" spans="1:1">
+    <row r="284" hidden="1" spans="1:1">
       <c r="A284" s="1" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="285" spans="1:1">
+    <row r="285" hidden="1" spans="1:1">
       <c r="A285" s="1" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="286" spans="1:1">
+    <row r="286" hidden="1" spans="1:1">
       <c r="A286" s="1" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="287" spans="1:1">
+    <row r="287" hidden="1" spans="1:1">
       <c r="A287" s="1" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="288" spans="1:1">
+    <row r="288" hidden="1" spans="1:1">
       <c r="A288" s="1" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="289" spans="1:1">
+    <row r="289" hidden="1" spans="1:1">
       <c r="A289" s="1" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="290" spans="1:1">
+    <row r="290" hidden="1" spans="1:1">
       <c r="A290" s="1" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="291" spans="1:1">
+    <row r="291" hidden="1" spans="1:1">
       <c r="A291" s="1" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="292" spans="1:1">
+    <row r="292" hidden="1" spans="1:1">
       <c r="A292" s="1" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="293" spans="1:1">
+    <row r="293" hidden="1" spans="1:1">
       <c r="A293" s="1" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="294" spans="1:1">
-      <c r="A294" s="1" t="s">
+    <row r="294" hidden="1" spans="1:1">
+      <c r="A294" s="2" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="295" spans="1:1">
+    <row r="295" hidden="1" spans="1:1">
       <c r="A295" s="1" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="296" spans="1:1">
-      <c r="A296" s="1" t="s">
+    <row r="296" hidden="1" spans="1:1">
+      <c r="A296" s="2" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="297" spans="1:1">
+    <row r="297" hidden="1" spans="1:1">
       <c r="A297" s="1" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="298" spans="1:1">
+    <row r="298" hidden="1" spans="1:1">
       <c r="A298" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="299" spans="1:1">
+    <row r="299" hidden="1" spans="1:1">
       <c r="A299" s="1" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="300" spans="1:1">
+    <row r="300" hidden="1" spans="1:1">
       <c r="A300" s="1" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="301" spans="1:1">
+    <row r="301" hidden="1" spans="1:1">
       <c r="A301" s="1" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="302" spans="1:1">
+    <row r="302" hidden="1" spans="1:1">
       <c r="A302" s="1" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="303" spans="1:1">
+    <row r="303" hidden="1" spans="1:1">
       <c r="A303" s="1" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="304" spans="1:1">
-      <c r="A304" s="1" t="s">
+    <row r="304" hidden="1" spans="1:1">
+      <c r="A304" s="2" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="305" spans="1:1">
+    <row r="305" hidden="1" spans="1:1">
       <c r="A305" s="1" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="306" spans="1:1">
+    <row r="306" hidden="1" spans="1:1">
       <c r="A306" s="1" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="307" spans="1:1">
+    <row r="307" hidden="1" spans="1:1">
       <c r="A307" s="1" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="308" spans="1:1">
+    <row r="308" hidden="1" spans="1:1">
       <c r="A308" s="1" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="309" spans="1:1">
+    <row r="309" hidden="1" spans="1:1">
       <c r="A309" s="1" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="310" spans="1:1">
+    <row r="310" hidden="1" spans="1:1">
       <c r="A310" s="1" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="311" spans="1:1">
+    <row r="311" hidden="1" spans="1:1">
       <c r="A311" s="1" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="312" spans="1:1">
+    <row r="312" hidden="1" spans="1:1">
       <c r="A312" s="1" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="313" spans="1:1">
+    <row r="313" hidden="1" spans="1:1">
       <c r="A313" s="1" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="314" spans="1:1">
+    <row r="314" hidden="1" spans="1:1">
       <c r="A314" s="1" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="315" spans="1:1">
+    <row r="315" hidden="1" spans="1:1">
       <c r="A315" s="1" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="316" spans="1:1">
+    <row r="316" hidden="1" spans="1:1">
       <c r="A316" s="1" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="317" spans="1:1">
+    <row r="317" hidden="1" spans="1:1">
       <c r="A317" s="1" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="318" spans="1:1">
+    <row r="318" hidden="1" spans="1:1">
       <c r="A318" s="1" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="319" spans="1:1">
+    <row r="319" hidden="1" spans="1:1">
       <c r="A319" s="1" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="320" spans="1:1">
+    <row r="320" hidden="1" spans="1:1">
       <c r="A320" s="1" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="321" spans="1:1">
+    <row r="321" hidden="1" spans="1:1">
       <c r="A321" s="1" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="322" spans="1:1">
+    <row r="322" hidden="1" spans="1:1">
       <c r="A322" s="1" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="323" spans="1:1">
+    <row r="323" hidden="1" spans="1:1">
       <c r="A323" s="1" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="324" spans="1:1">
+    <row r="324" hidden="1" spans="1:1">
       <c r="A324" s="1" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="325" spans="1:1">
+    <row r="325" hidden="1" spans="1:1">
       <c r="A325" s="1" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="326" spans="1:1">
+    <row r="326" hidden="1" spans="1:1">
       <c r="A326" s="1" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="327" spans="1:1">
+    <row r="327" hidden="1" spans="1:1">
       <c r="A327" s="1" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="328" spans="1:1">
+    <row r="328" hidden="1" spans="1:1">
       <c r="A328" s="1" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="329" spans="1:1">
+    <row r="329" hidden="1" spans="1:1">
       <c r="A329" s="1" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="330" spans="1:1">
+    <row r="330" hidden="1" spans="1:1">
       <c r="A330" s="1" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="331" spans="1:1">
+    <row r="331" hidden="1" spans="1:1">
       <c r="A331" s="1" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="332" spans="1:1">
+    <row r="332" hidden="1" spans="1:1">
       <c r="A332" s="1" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="333" spans="1:1">
+    <row r="333" hidden="1" spans="1:1">
       <c r="A333" s="1" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="334" spans="1:1">
+    <row r="334" hidden="1" spans="1:1">
       <c r="A334" s="1" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="335" spans="1:1">
+    <row r="335" hidden="1" spans="1:1">
       <c r="A335" s="1" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="336" spans="1:1">
+    <row r="336" hidden="1" spans="1:1">
       <c r="A336" s="1" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="337" spans="1:1">
+    <row r="337" hidden="1" spans="1:1">
       <c r="A337" s="1" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="338" spans="1:1">
+    <row r="338" hidden="1" spans="1:1">
       <c r="A338" s="1" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="339" spans="1:1">
+    <row r="339" hidden="1" spans="1:1">
       <c r="A339" s="1" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="340" spans="1:1">
+    <row r="340" hidden="1" spans="1:1">
       <c r="A340" s="1" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="341" spans="1:1">
+    <row r="341" hidden="1" spans="1:1">
       <c r="A341" s="1" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="342" spans="1:1">
+    <row r="342" hidden="1" spans="1:1">
       <c r="A342" s="1" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="343" spans="1:1">
+    <row r="343" hidden="1" spans="1:1">
       <c r="A343" s="1" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="344" spans="1:1">
+    <row r="344" hidden="1" spans="1:1">
       <c r="A344" s="1" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="345" spans="1:1">
+    <row r="345" hidden="1" spans="1:1">
       <c r="A345" s="1" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="346" spans="1:1">
+    <row r="346" hidden="1" spans="1:1">
       <c r="A346" s="1" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="347" spans="1:1">
+    <row r="347" hidden="1" spans="1:1">
       <c r="A347" s="1" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="348" spans="1:1">
+    <row r="348" hidden="1" spans="1:1">
       <c r="A348" s="1" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="349" spans="1:1">
+    <row r="349" hidden="1" spans="1:1">
       <c r="A349" s="1" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="350" spans="1:1">
+    <row r="350" hidden="1" spans="1:1">
       <c r="A350" s="1" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="351" spans="1:1">
+    <row r="351" hidden="1" spans="1:1">
       <c r="A351" s="1" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="352" spans="1:1">
+    <row r="352" hidden="1" spans="1:1">
       <c r="A352" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="353" spans="1:1">
+    <row r="353" hidden="1" spans="1:1">
       <c r="A353" s="1" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="354" spans="1:1">
+    <row r="354" hidden="1" spans="1:1">
       <c r="A354" s="1" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="355" spans="1:1">
+    <row r="355" hidden="1" spans="1:1">
       <c r="A355" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="356" spans="1:1">
+    <row r="356" hidden="1" spans="1:1">
       <c r="A356" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="357" spans="1:1">
+    <row r="357" hidden="1" spans="1:1">
       <c r="A357" s="1" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="358" spans="1:1">
-      <c r="A358" s="1" t="s">
+    <row r="358" hidden="1" spans="1:1">
+      <c r="A358" s="2" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="359" spans="1:1">
+    <row r="359" hidden="1" spans="1:1">
       <c r="A359" s="1" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="360" spans="1:1">
+    <row r="360" hidden="1" spans="1:1">
       <c r="A360" s="1" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="361" spans="1:1">
+    <row r="361" hidden="1" spans="1:1">
       <c r="A361" s="1" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="362" spans="1:1">
+    <row r="362" hidden="1" spans="1:1">
       <c r="A362" s="1" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="363" spans="1:1">
+    <row r="363" hidden="1" spans="1:1">
       <c r="A363" s="1" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="364" spans="1:1">
+    <row r="364" hidden="1" spans="1:1">
       <c r="A364" s="1" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="365" spans="1:1">
+    <row r="365" hidden="1" spans="1:1">
       <c r="A365" s="1" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="366" spans="1:1">
+    <row r="366" hidden="1" spans="1:1">
       <c r="A366" s="1" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="367" spans="1:1">
+    <row r="367" hidden="1" spans="1:1">
       <c r="A367" s="1" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="368" spans="1:1">
+    <row r="368" hidden="1" spans="1:1">
       <c r="A368" s="1" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="369" spans="1:1">
+    <row r="369" hidden="1" spans="1:1">
       <c r="A369" s="1" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="370" spans="1:1">
+    <row r="370" hidden="1" spans="1:1">
       <c r="A370" s="1" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="371" spans="1:1">
+    <row r="371" hidden="1" spans="1:1">
       <c r="A371" s="1" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="372" spans="1:1">
+    <row r="372" hidden="1" spans="1:1">
       <c r="A372" s="1" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="373" spans="1:1">
+    <row r="373" hidden="1" spans="1:1">
       <c r="A373" s="1" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="374" spans="1:1">
+    <row r="374" hidden="1" spans="1:1">
       <c r="A374" s="1" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="375" spans="1:1">
+    <row r="375" hidden="1" spans="1:1">
       <c r="A375" s="1" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="376" spans="1:1">
+    <row r="376" hidden="1" spans="1:1">
       <c r="A376" s="1" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="377" spans="1:1">
+    <row r="377" hidden="1" spans="1:1">
       <c r="A377" s="1" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="378" spans="1:1">
+    <row r="378" hidden="1" spans="1:1">
       <c r="A378" s="1" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="379" spans="1:1">
+    <row r="379" hidden="1" spans="1:1">
       <c r="A379" s="1" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="380" spans="1:1">
+    <row r="380" hidden="1" spans="1:1">
       <c r="A380" s="1" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="381" spans="1:1">
+    <row r="381" hidden="1" spans="1:1">
       <c r="A381" s="1" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="382" spans="1:1">
+    <row r="382" hidden="1" spans="1:1">
       <c r="A382" s="1" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="383" spans="1:1">
+    <row r="383" hidden="1" spans="1:1">
       <c r="A383" s="1" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="384" spans="1:1">
+    <row r="384" hidden="1" spans="1:1">
       <c r="A384" s="1" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="385" spans="1:1">
+    <row r="385" hidden="1" spans="1:1">
       <c r="A385" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="386" spans="1:1">
+    <row r="386" hidden="1" spans="1:1">
       <c r="A386" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="387" spans="1:1">
+    <row r="387" hidden="1" spans="1:1">
       <c r="A387" s="1" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="388" spans="1:1">
-      <c r="A388" s="1" t="s">
+    <row r="388" hidden="1" spans="1:1">
+      <c r="A388" s="2" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="389" spans="1:1">
+    <row r="389" hidden="1" spans="1:1">
       <c r="A389" s="1" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="390" spans="1:1">
+    <row r="390" hidden="1" spans="1:1">
       <c r="A390" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="391" spans="1:1">
+    <row r="391" hidden="1" spans="1:1">
       <c r="A391" s="1" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="392" spans="1:1">
+    <row r="392" hidden="1" spans="1:1">
       <c r="A392" s="1" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="393" spans="1:1">
-      <c r="A393" s="1" t="s">
+    <row r="393" hidden="1" spans="1:1">
+      <c r="A393" s="2" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="394" spans="1:1">
+    <row r="394" hidden="1" spans="1:1">
       <c r="A394" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="395" spans="1:1">
+    <row r="395" hidden="1" spans="1:1">
       <c r="A395" s="1" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="396" spans="1:1">
+    <row r="396" hidden="1" spans="1:1">
       <c r="A396" s="1" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="397" spans="1:1">
+    <row r="397" hidden="1" spans="1:1">
       <c r="A397" s="1" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="398" spans="1:1">
+    <row r="398" hidden="1" spans="1:1">
       <c r="A398" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="399" spans="1:1">
+    <row r="399" hidden="1" spans="1:1">
       <c r="A399" s="1" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="400" spans="1:1">
-      <c r="A400" s="1" t="s">
+    <row r="400" hidden="1" spans="1:1">
+      <c r="A400" s="2" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="401" spans="1:1">
+    <row r="401" hidden="1" spans="1:1">
       <c r="A401" s="1" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="402" spans="1:1">
+    <row r="402" hidden="1" spans="1:1">
       <c r="A402" s="1" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="403" spans="1:1">
+    <row r="403" hidden="1" spans="1:1">
       <c r="A403" s="1" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="404" spans="1:1">
-      <c r="A404" s="1" t="s">
+    <row r="404" hidden="1" spans="1:1">
+      <c r="A404" s="2" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="405" spans="1:1">
+    <row r="405" hidden="1" spans="1:1">
       <c r="A405" s="1" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="406" spans="1:1">
+    <row r="406" hidden="1" spans="1:1">
       <c r="A406" s="1" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="407" spans="1:1">
+    <row r="407" hidden="1" spans="1:1">
       <c r="A407" s="1" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="408" spans="1:1">
+    <row r="408" hidden="1" spans="1:1">
       <c r="A408" s="1" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="409" spans="1:1">
+    <row r="409" hidden="1" spans="1:1">
       <c r="A409" s="1" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="410" spans="1:1">
+    <row r="410" hidden="1" spans="1:1">
       <c r="A410" s="1" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="411" spans="1:1">
+    <row r="411" hidden="1" spans="1:1">
       <c r="A411" s="1" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="412" spans="1:1">
+    <row r="412" hidden="1" spans="1:1">
       <c r="A412" s="1" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="413" spans="1:1">
+    <row r="413" hidden="1" spans="1:1">
       <c r="A413" s="1" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="414" spans="1:1">
+    <row r="414" hidden="1" spans="1:1">
       <c r="A414" s="1" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="415" spans="1:1">
+    <row r="415" hidden="1" spans="1:1">
       <c r="A415" s="1" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="416" spans="1:1">
+    <row r="416" hidden="1" spans="1:1">
       <c r="A416" s="1" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="417" spans="1:1">
+    <row r="417" hidden="1" spans="1:1">
       <c r="A417" s="1" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="418" spans="1:1">
-      <c r="A418" s="2" t="s">
+    <row r="418" hidden="1" spans="1:1">
+      <c r="A418" s="1" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="419" spans="1:1">
-      <c r="A419" s="2" t="s">
+    <row r="419" hidden="1" spans="1:1">
+      <c r="A419" s="1" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="420" spans="1:1">
-      <c r="A420" s="2" t="s">
+    <row r="420" hidden="1" spans="1:1">
+      <c r="A420" s="1" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="421" spans="1:1">
-      <c r="A421" s="2" t="s">
+    <row r="421" hidden="1" spans="1:1">
+      <c r="A421" s="1" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="422" spans="1:1">
-      <c r="A422" s="2" t="s">
+    <row r="422" hidden="1" spans="1:1">
+      <c r="A422" s="1" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="423" spans="1:1">
-      <c r="A423" s="2" t="s">
+    <row r="423" hidden="1" spans="1:1">
+      <c r="A423" s="1" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="424" spans="1:1">
-      <c r="A424" s="2" t="s">
+    <row r="424" hidden="1" spans="1:1">
+      <c r="A424" s="1" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="425" spans="1:1">
-      <c r="A425" s="2" t="s">
+    <row r="425" hidden="1" spans="1:1">
+      <c r="A425" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="426" spans="1:1">
-      <c r="A426" s="2" t="s">
+    <row r="426" hidden="1" spans="1:1">
+      <c r="A426" s="1" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="427" spans="1:1">
-      <c r="A427" s="2" t="s">
+    <row r="427" hidden="1" spans="1:1">
+      <c r="A427" s="1" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="428" spans="1:1">
-      <c r="A428" s="2" t="s">
+    <row r="428" hidden="1" spans="1:1">
+      <c r="A428" s="1" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="429" spans="1:1">
-      <c r="A429" s="2" t="s">
+    <row r="429" hidden="1" spans="1:1">
+      <c r="A429" s="1" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="430" spans="1:1">
-      <c r="A430" s="2" t="s">
+    <row r="430" hidden="1" spans="1:1">
+      <c r="A430" s="1" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="431" spans="1:1">
-      <c r="A431" s="2" t="s">
+    <row r="431" hidden="1" spans="1:1">
+      <c r="A431" s="1" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="432" spans="1:1">
-      <c r="A432" s="2" t="s">
+    <row r="432" hidden="1" spans="1:1">
+      <c r="A432" s="1" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="433" spans="1:1">
-      <c r="A433" s="2" t="s">
+    <row r="433" hidden="1" spans="1:1">
+      <c r="A433" s="1" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="434" spans="1:1">
-      <c r="A434" s="2" t="s">
+    <row r="434" hidden="1" spans="1:1">
+      <c r="A434" s="1" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="435" spans="1:1">
-      <c r="A435" s="2" t="s">
+    <row r="435" hidden="1" spans="1:1">
+      <c r="A435" s="1" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="436" spans="1:1">
-      <c r="A436" s="2" t="s">
+    <row r="436" hidden="1" spans="1:1">
+      <c r="A436" s="1" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="437" spans="1:1">
-      <c r="A437" s="2" t="s">
+    <row r="437" hidden="1" spans="1:1">
+      <c r="A437" s="1" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="438" spans="1:1">
-      <c r="A438" s="2" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="439" spans="1:1">
-      <c r="A439" s="2" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="440" spans="1:1">
-      <c r="A440" s="2" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="441" spans="1:1">
-      <c r="A441" s="2" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="442" spans="1:1">
-      <c r="A442" s="2" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="443" spans="1:1">
-      <c r="A443" s="2" t="s">
-        <v>442</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:A437" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="0">
+      <customFilters>
+        <customFilter operator="equal" val="*sh5*"/>
+        <customFilter operator="equal" val="*sh399*"/>
+      </customFilters>
+    </filterColumn>
+    <sortState ref="A2:A437">
+      <sortCondition ref="A2"/>
+    </sortState>
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
